--- a/datos_control/HPO_codigo_nombre.xlsx
+++ b/datos_control/HPO_codigo_nombre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\codigo_TFM\Generacion_librerias_IA_prediccion_ciliopatias\datos_control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065C2A5D-1EF4-4750-AFBA-571E26ECBBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE8A925-8C68-4417-8697-9CA9F4A1505B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3538,18 +3538,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -3579,15 +3573,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3921,7 +3913,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3935,7 +3927,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1144</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3948,8 +3940,8 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>1145</v>
+      <c r="D4" s="3" t="s">
+        <v>1156</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3991,7 +3983,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4130,7 +4122,7 @@
       <c r="C17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>1156</v>
       </c>
     </row>
@@ -4144,8 +4136,8 @@
       <c r="C18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>1150</v>
+      <c r="D18" s="3" t="s">
+        <v>1156</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -4186,8 +4178,8 @@
       <c r="C21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>1156</v>
+      <c r="D21" s="3" t="s">
+        <v>1148</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -4242,7 +4234,7 @@
       <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>1151</v>
       </c>
     </row>
@@ -4256,7 +4248,7 @@
       <c r="C26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>1156</v>
       </c>
     </row>
@@ -4592,7 +4584,7 @@
       <c r="C50" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="3" t="s">
         <v>1147</v>
       </c>
     </row>
@@ -4634,7 +4626,7 @@
       <c r="C53" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="3" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -4928,7 +4920,7 @@
       <c r="C74" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="3" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -4942,7 +4934,7 @@
       <c r="C75" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="3" t="s">
         <v>1158</v>
       </c>
     </row>
@@ -5306,7 +5298,7 @@
       <c r="C101" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" s="3" t="s">
         <v>1152</v>
       </c>
     </row>
@@ -5335,7 +5327,7 @@
         <v>206</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1145</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -5419,7 +5411,7 @@
         <v>218</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1145</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -5474,7 +5466,7 @@
       <c r="C113" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D113" s="5" t="s">
+      <c r="D113" s="3" t="s">
         <v>1148</v>
       </c>
     </row>
@@ -5825,7 +5817,7 @@
         <v>276</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -6162,7 +6154,7 @@
         <v>324</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -6344,7 +6336,7 @@
         <v>350</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -6596,7 +6588,7 @@
         <v>386</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>1159</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -6778,7 +6770,7 @@
         <v>412</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>1156</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -7114,7 +7106,7 @@
         <v>460</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -7310,7 +7302,7 @@
         <v>488</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -7352,7 +7344,7 @@
         <v>494</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>1159</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -7366,7 +7358,7 @@
         <v>496</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -7562,7 +7554,7 @@
         <v>524</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -7632,7 +7624,7 @@
         <v>534</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>1150</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -7688,7 +7680,7 @@
         <v>542</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>1159</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -8024,7 +8016,7 @@
         <v>590</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -8094,7 +8086,7 @@
         <v>600</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -8122,7 +8114,7 @@
         <v>604</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -8262,7 +8254,7 @@
         <v>624</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -8360,7 +8352,7 @@
         <v>638</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -8542,7 +8534,7 @@
         <v>664</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -8668,7 +8660,7 @@
         <v>682</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -8752,7 +8744,7 @@
         <v>694</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -8948,7 +8940,7 @@
         <v>722</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -8990,7 +8982,7 @@
         <v>728</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -9060,7 +9052,7 @@
         <v>738</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1147</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -9144,7 +9136,7 @@
         <v>750</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>750</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -9200,7 +9192,7 @@
         <v>758</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -9242,7 +9234,7 @@
         <v>764</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1145</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -9256,7 +9248,7 @@
         <v>766</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -9382,7 +9374,7 @@
         <v>784</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -9452,7 +9444,7 @@
         <v>794</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -9522,7 +9514,7 @@
         <v>804</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -9662,7 +9654,7 @@
         <v>824</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1156</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -9676,7 +9668,7 @@
         <v>826</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -9788,7 +9780,7 @@
         <v>842</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -9858,7 +9850,7 @@
         <v>852</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -9914,7 +9906,7 @@
         <v>860</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
@@ -9956,7 +9948,7 @@
         <v>866</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
@@ -10012,7 +10004,7 @@
         <v>874</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -10068,7 +10060,7 @@
         <v>882</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
@@ -10530,7 +10522,7 @@
         <v>948</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -10726,7 +10718,7 @@
         <v>976</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
@@ -10852,7 +10844,7 @@
         <v>994</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
@@ -10866,7 +10858,7 @@
         <v>996</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>996</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
@@ -10950,7 +10942,7 @@
         <v>1008</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -10964,7 +10956,7 @@
         <v>1010</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
@@ -10978,7 +10970,7 @@
         <v>1012</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
@@ -11202,7 +11194,7 @@
         <v>1044</v>
       </c>
       <c r="D522" s="3" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
@@ -11230,7 +11222,7 @@
         <v>1048</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
@@ -11244,7 +11236,7 @@
         <v>1050</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
@@ -11300,7 +11292,7 @@
         <v>1058</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
@@ -11580,7 +11572,7 @@
         <v>1098</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
@@ -11608,7 +11600,7 @@
         <v>1102</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
@@ -11846,7 +11838,7 @@
         <v>1136</v>
       </c>
       <c r="D568" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
